--- a/corr_matrix/residual_exam4A_3PL.xlsx
+++ b/corr_matrix/residual_exam4A_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4A02</t>
@@ -565,76 +570,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06846107430457864</v>
+        <v>0.04546137095443818</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08666994376242819</v>
+        <v>-0.0728792631560732</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09350343267988966</v>
+        <v>0.1170602101571619</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.110955812116737</v>
+        <v>-0.1115949833249103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1419161730266243</v>
+        <v>0.1248129502023219</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04273641660201171</v>
+        <v>0.001059094107962507</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05639057148288738</v>
+        <v>0.1049694826395912</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.07322485568216565</v>
+        <v>-0.1163253331015127</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.04418808715523136</v>
+        <v>-0.0665922429224677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09862022865428051</v>
+        <v>0.09884642445237674</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01407176240888758</v>
+        <v>0.003159583858542053</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01553401393241825</v>
+        <v>-0.003396478924864653</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005655748719153023</v>
+        <v>-0.002779112297835135</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06239619098432448</v>
+        <v>-0.009540263633854828</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2642256559546799</v>
+        <v>-0.2554282692008578</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1115793390247838</v>
+        <v>-0.1021592610201006</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03054837910556359</v>
+        <v>-0.06410689608143566</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2721094632221182</v>
+        <v>-0.2611878242447249</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1057033273050682</v>
+        <v>-0.1058716071754058</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1142298174413352</v>
+        <v>-0.08130713382084868</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1283990469538358</v>
+        <v>-0.1156483488664906</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03267497664441223</v>
+        <v>-0.029433496549341</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2520675978436042</v>
+        <v>-0.2207260158334451</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.06525572386233182</v>
+        <v>-0.1341674741568012</v>
       </c>
     </row>
     <row r="3">
@@ -644,79 +649,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06846107430457864</v>
+        <v>0.04546137095443818</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.102865979770051</v>
+        <v>-0.1069465751097201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03666044351225335</v>
+        <v>0.03328627802709998</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02848326328363445</v>
+        <v>0.02683940281514414</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.02386704279622004</v>
+        <v>-0.05730494050629265</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2553548539379507</v>
+        <v>-0.2368126396180127</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.005073898189067237</v>
+        <v>-0.008768449211736624</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1699776162174561</v>
+        <v>0.1128681325734688</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.07633814837194282</v>
+        <v>-0.1040597583668818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008075183346199107</v>
+        <v>-0.00807987682108673</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.008087397267235332</v>
+        <v>-0.05050288270213034</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1477414665567885</v>
+        <v>-0.1643578835791269</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07523970361239991</v>
+        <v>-0.105278274886355</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.03279852099146682</v>
+        <v>-0.02088983030982909</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.009884059232415497</v>
+        <v>-0.0362056615885367</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01330990901069238</v>
+        <v>-0.01256893607328853</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2669242233955899</v>
+        <v>0.07405696530474856</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06784863835372863</v>
+        <v>-0.08791220084457049</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.02614132734557088</v>
+        <v>-0.05206028030497072</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1391142918175761</v>
+        <v>-0.1292729791903385</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.06310892628439439</v>
+        <v>-0.08160400171389084</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0325681507773059</v>
+        <v>-0.0601361082288161</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1650420717119973</v>
+        <v>-0.1584312442011695</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.08653404935448977</v>
+        <v>-0.1092641382210543</v>
       </c>
     </row>
     <row r="4">
@@ -726,79 +731,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08666994376242819</v>
+        <v>-0.0728792631560732</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.102865979770051</v>
+        <v>-0.1069465751097201</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05953983754226225</v>
+        <v>-0.05429548004926237</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.03575646542396749</v>
+        <v>-0.03927441269930323</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09366311467501859</v>
+        <v>-0.1128055893420937</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02471848790800469</v>
+        <v>0.0156957072379858</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05188490954242046</v>
+        <v>-0.001133558128134159</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2347745524477818</v>
+        <v>-0.2691526515563917</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.06423576279571704</v>
+        <v>-0.08820004287011665</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1236217135623715</v>
+        <v>0.1171682225491686</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0342303305104906</v>
+        <v>-0.03038730479569061</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1243080758968476</v>
+        <v>-0.116244015524032</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1527020796631762</v>
+        <v>0.151238648892354</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004746345049572657</v>
+        <v>0.05545885841468199</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1596506218579032</v>
+        <v>-0.1345390465847611</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3652684903218418</v>
+        <v>-0.326573467036564</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.001168786775782443</v>
+        <v>-0.06600683732890779</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1098417375980897</v>
+        <v>0.1239915997002966</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1142290661976083</v>
+        <v>-0.1175758073771253</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3125273264741198</v>
+        <v>-0.2639081178532762</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1303628752636095</v>
+        <v>0.1381469127455254</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09366466586728024</v>
+        <v>0.1040410638966982</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1483978835371393</v>
+        <v>0.1741072247040596</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03769113220606555</v>
+        <v>-0.1381433661314109</v>
       </c>
     </row>
     <row r="5">
@@ -808,79 +813,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09350343267988966</v>
+        <v>0.1170602101571619</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03666044351225335</v>
+        <v>0.03328627802709998</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05953983754226225</v>
+        <v>-0.05429548004926237</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3081854214332834</v>
+        <v>0.1893655959594531</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1427519123781501</v>
+        <v>-0.1416874345288294</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01298734283167897</v>
+        <v>0.003036810041929431</v>
       </c>
       <c r="I5" t="n">
-        <v>0.215404077973244</v>
+        <v>0.2342052310273085</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1903934609774232</v>
+        <v>-0.1810622576184385</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2469017435675677</v>
+        <v>0.2485302893245329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07606258200764628</v>
+        <v>0.04284206751232603</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05935459940157483</v>
+        <v>0.08371126904946226</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.204303144622789</v>
+        <v>-0.211270508893957</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1884037136266725</v>
+        <v>0.1690754715674055</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05937596725925919</v>
+        <v>-0.07374182133121257</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03939947066283963</v>
+        <v>0.04432931012438374</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07733174147292698</v>
+        <v>0.07640183918839215</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1356757383688977</v>
+        <v>-0.1101320671514192</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2039408881056791</v>
+        <v>0.1702869188538705</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.242548939420619</v>
+        <v>-0.2639045560333244</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1524956806022614</v>
+        <v>-0.1469323170959278</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3667370445127645</v>
+        <v>-0.3826720789498251</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07274049467139727</v>
+        <v>0.07418123108440784</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1484258321862043</v>
+        <v>-0.1402427128490653</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.04848076034591595</v>
+        <v>0.01068755160722421</v>
       </c>
     </row>
     <row r="6">
@@ -890,79 +895,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.110955812116737</v>
+        <v>-0.1115949833249103</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02848326328363445</v>
+        <v>0.02683940281514414</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03575646542396749</v>
+        <v>-0.03927441269930323</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3081854214332834</v>
+        <v>0.1893655959594531</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06229285978379715</v>
+        <v>-0.08914267169373399</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2129004617141146</v>
+        <v>-0.2637471052679627</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09860193139248852</v>
+        <v>-0.1411212369941517</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1416806965679333</v>
+        <v>-0.1434248266088301</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002779187207143664</v>
+        <v>-0.03704576184350808</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153100111285747</v>
+        <v>0.09188354628881726</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1596648150059053</v>
+        <v>-0.1673505764017314</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07297331408742871</v>
+        <v>-0.1229566269568241</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1733949111304422</v>
+        <v>0.1504613701187739</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2471912202703344</v>
+        <v>0.2280079477596407</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04163575432286039</v>
+        <v>0.04058511471636007</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06125521483073013</v>
+        <v>0.0620620846008112</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2961336219084621</v>
+        <v>0.1476940177145023</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2035802865464004</v>
+        <v>0.1619964973706571</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1087047597598104</v>
+        <v>-0.1691567807682262</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.09487991186943991</v>
+        <v>-0.1079007107644815</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03320538397405379</v>
+        <v>0.004866338952331471</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07293333438927646</v>
+        <v>0.06742330807065183</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.07508356364663261</v>
+        <v>-0.09375754423229749</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.02284565087764485</v>
+        <v>0.008465930079086728</v>
       </c>
     </row>
     <row r="7">
@@ -972,79 +977,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1419161730266243</v>
+        <v>0.1248129502023219</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.02386704279622004</v>
+        <v>-0.05730494050629265</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09366311467501859</v>
+        <v>-0.1128055893420937</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1427519123781501</v>
+        <v>-0.1416874345288294</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06229285978379715</v>
+        <v>-0.08914267169373399</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.007997129685387407</v>
+        <v>0.015860965755756</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2083473256458045</v>
+        <v>-0.1451764674268717</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07373580890256502</v>
+        <v>-0.09296085462353765</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1195270287788545</v>
+        <v>0.09304785356547382</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05607114024853614</v>
+        <v>-0.05544779960971468</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1792501739669181</v>
+        <v>-0.2058990432493887</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05308321858780132</v>
+        <v>-0.0563967360925801</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.05736284762055232</v>
+        <v>-0.0873071141165865</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03026885825778066</v>
+        <v>0.04883574954483194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1273479183509752</v>
+        <v>-0.1432489993336261</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02025442684803875</v>
+        <v>-0.00452445950181703</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1062525123426599</v>
+        <v>0.1236900071107781</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1395559674126733</v>
+        <v>-0.1603512580397853</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.25066660898599</v>
+        <v>-0.2763621633747501</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.07676344073232731</v>
+        <v>-0.08971142734917244</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1525620104773109</v>
+        <v>0.1525065921900172</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2026430399487932</v>
+        <v>-0.2219472019119165</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01445641311303298</v>
+        <v>0.01235105852821646</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.02084473619392829</v>
+        <v>-0.06480687681912249</v>
       </c>
     </row>
     <row r="8">
@@ -1054,79 +1059,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.04273641660201171</v>
+        <v>0.001059094107962507</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2553548539379507</v>
+        <v>-0.2368126396180127</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02471848790800469</v>
+        <v>0.0156957072379858</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01298734283167897</v>
+        <v>0.003036810041929431</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2129004617141146</v>
+        <v>-0.2637471052679627</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.007997129685387407</v>
+        <v>0.015860965755756</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2009136345074513</v>
+        <v>-0.1230884443925479</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1935571978129813</v>
+        <v>-0.1980660668290664</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08726892479776326</v>
+        <v>0.08569775433477013</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005209416048828825</v>
+        <v>0.01886540792254561</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01491960008246996</v>
+        <v>0.02876103255193571</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008556450581249589</v>
+        <v>0.02000530832501556</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3309972341733941</v>
+        <v>0.333428578416301</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00279285414910758</v>
+        <v>0.03778354275267801</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1727674396077316</v>
+        <v>-0.1249044387211418</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2182026237715462</v>
+        <v>-0.1777530046403147</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1916525319306796</v>
+        <v>-0.2657375093407782</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08587297415235542</v>
+        <v>0.08066034443584041</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1113668570528427</v>
+        <v>0.1113597264011574</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1405695950946956</v>
+        <v>0.1556914280446103</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1064125475694993</v>
+        <v>-0.08361823886933628</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3451352046263638</v>
+        <v>-0.308037088935587</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1120414616068364</v>
+        <v>0.1311271106285613</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.08278260237290894</v>
+        <v>-0.1182930324070627</v>
       </c>
     </row>
     <row r="9">
@@ -1136,79 +1141,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05639057148288738</v>
+        <v>0.1049694826395912</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.005073898189067237</v>
+        <v>-0.008768449211736624</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05188490954242046</v>
+        <v>-0.001133558128134159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.215404077973244</v>
+        <v>0.2342052310273085</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09860193139248852</v>
+        <v>-0.1411212369941517</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2083473256458045</v>
+        <v>-0.1451764674268717</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2009136345074513</v>
+        <v>-0.1230884443925479</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.09488314430471703</v>
+        <v>-0.1056059915849355</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09567170786943859</v>
+        <v>-0.07135332959119089</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.03392666424819465</v>
+        <v>0.006773937896868157</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04515367010318804</v>
+        <v>0.0116598718925679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2645282050388944</v>
+        <v>-0.209616388299066</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01162054789011406</v>
+        <v>0.04058994821967726</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.05604576962883703</v>
+        <v>0.01847241792046498</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2320282430384998</v>
+        <v>0.2749038422466645</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1216443129806212</v>
+        <v>0.1354265045104489</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1941125033118677</v>
+        <v>-0.3261339621557808</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1541690587360727</v>
+        <v>-0.123285981019245</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1436164437751536</v>
+        <v>-0.1089409202440981</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.014895259375718</v>
+        <v>0.02786153280055019</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3748112424556149</v>
+        <v>-0.2999498258179474</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1767747392059384</v>
+        <v>0.2198549784779854</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0826535155641706</v>
+        <v>-0.02398004170597763</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1442935911488702</v>
+        <v>-0.1451779590810106</v>
       </c>
     </row>
     <row r="10">
@@ -1218,79 +1223,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.07322485568216565</v>
+        <v>-0.1163253331015127</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1699776162174561</v>
+        <v>0.1128681325734688</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2347745524477818</v>
+        <v>-0.2691526515563917</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1903934609774232</v>
+        <v>-0.1810622576184385</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1416806965679333</v>
+        <v>-0.1434248266088301</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07373580890256502</v>
+        <v>-0.09296085462353765</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1935571978129813</v>
+        <v>-0.1980660668290664</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09488314430471703</v>
+        <v>-0.1056059915849355</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04121515807463631</v>
+        <v>-0.06914299273683522</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.07674934717927898</v>
+        <v>-0.09068823483529329</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07250107307379867</v>
+        <v>0.0191946372788004</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09562412730446343</v>
+        <v>0.06725138946045521</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3120693531502823</v>
+        <v>-0.3419733863567689</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2474185011720835</v>
+        <v>-0.2588978531092331</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.06150477941428651</v>
+        <v>0.005789445129930656</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03789670336620722</v>
+        <v>-0.01978400455434953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2353022320337063</v>
+        <v>0.2278883700378315</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0394918760778257</v>
+        <v>0.005438300193768845</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2487036336732334</v>
+        <v>0.2153853175853401</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1466227388328502</v>
+        <v>0.09925825500038475</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03584881566329622</v>
+        <v>0.00482752895915282</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.10688462729661</v>
+        <v>-0.1476541273146562</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1231712329800701</v>
+        <v>-0.1487430310115122</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.06005872321767792</v>
+        <v>0.1431949440172071</v>
       </c>
     </row>
     <row r="11">
@@ -1300,79 +1305,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.04418808715523136</v>
+        <v>-0.0665922429224677</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.07633814837194282</v>
+        <v>-0.1040597583668818</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.06423576279571704</v>
+        <v>-0.08820004287011665</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2469017435675677</v>
+        <v>0.2485302893245329</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.002779187207143664</v>
+        <v>-0.03704576184350808</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1195270287788545</v>
+        <v>0.09304785356547382</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08726892479776326</v>
+        <v>0.08569775433477013</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09567170786943859</v>
+        <v>-0.07135332959119089</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.04121515807463631</v>
+        <v>-0.06914299273683522</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4050656860936254</v>
+        <v>0.3862361009820047</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1506707688688718</v>
+        <v>-0.1891728094503962</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03345736028417445</v>
+        <v>-0.003381483125568192</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09491633747282543</v>
+        <v>0.04254490698463638</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1145209701825497</v>
+        <v>-0.1151294319029593</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.003501930630200548</v>
+        <v>-0.02640181206166841</v>
       </c>
       <c r="R11" t="n">
-        <v>0.05462772849810755</v>
+        <v>0.04130237446562691</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2348301045663445</v>
+        <v>0.1660198022867714</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03836728236635845</v>
+        <v>-0.008779392495777394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3057493593159705</v>
+        <v>-0.3809435574117781</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2065883818473965</v>
+        <v>-0.2345752253997641</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3123827828609161</v>
+        <v>-0.3485250494193273</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1256898600927265</v>
+        <v>0.09291841897282982</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.2243689674152028</v>
+        <v>-0.2539109220770367</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.1527679788991687</v>
+        <v>-0.05417102469947842</v>
       </c>
     </row>
     <row r="12">
@@ -1382,79 +1387,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09862022865428051</v>
+        <v>0.09884642445237674</v>
       </c>
       <c r="C12" t="n">
-        <v>0.008075183346199107</v>
+        <v>-0.00807987682108673</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1236217135623715</v>
+        <v>0.1171682225491686</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07606258200764628</v>
+        <v>0.04284206751232603</v>
       </c>
       <c r="F12" t="n">
-        <v>0.153100111285747</v>
+        <v>0.09188354628881726</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.05607114024853614</v>
+        <v>-0.05544779960971468</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005209416048828825</v>
+        <v>0.01886540792254561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03392666424819465</v>
+        <v>0.006773937896868157</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.07674934717927898</v>
+        <v>-0.09068823483529329</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4050656860936254</v>
+        <v>0.3862361009820047</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02696996619406405</v>
+        <v>0.02189360534237607</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04375379667711657</v>
+        <v>-0.06150793389800161</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.01590880241024032</v>
+        <v>-0.05446703898341512</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2026453869388183</v>
+        <v>-0.1917782991434748</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.0006348033128858367</v>
+        <v>-0.009015545844369772</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0253834451935978</v>
+        <v>0.01433628511027571</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1158068014172114</v>
+        <v>0.07932373537019947</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01931574660041992</v>
+        <v>-0.02107951123937241</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3012876912512547</v>
+        <v>-0.3465757365504366</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2876849930437493</v>
+        <v>-0.3023718356585228</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1724437781679148</v>
+        <v>-0.1823059053769813</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.03488712500007909</v>
+        <v>-0.0522783272541282</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3579994878714218</v>
+        <v>-0.3667157424923509</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.04283451957315779</v>
+        <v>0.03060519538109467</v>
       </c>
     </row>
     <row r="13">
@@ -1464,79 +1469,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01407176240888758</v>
+        <v>0.003159583858542053</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.008087397267235332</v>
+        <v>-0.05050288270213034</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0342303305104906</v>
+        <v>-0.03038730479569061</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05935459940157483</v>
+        <v>0.08371126904946226</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1596648150059053</v>
+        <v>-0.1673505764017314</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1792501739669181</v>
+        <v>-0.2058990432493887</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01491960008246996</v>
+        <v>0.02876103255193571</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04515367010318804</v>
+        <v>0.0116598718925679</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07250107307379867</v>
+        <v>0.0191946372788004</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1506707688688718</v>
+        <v>-0.1891728094503962</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02696996619406405</v>
+        <v>0.02189360534237607</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.009758001566214427</v>
+        <v>-0.00355459600083354</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.126151370615202</v>
+        <v>-0.1431576596393079</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08888540727027135</v>
+        <v>-0.03699917494537475</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1403713156891874</v>
+        <v>-0.1428650279191456</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.03650317742160974</v>
+        <v>-0.04195125954244813</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0779738025129382</v>
+        <v>-0.08695806718091306</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1041292160397365</v>
+        <v>-0.0980968938908678</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1235280895570446</v>
+        <v>0.1236009637655076</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.07425815230967063</v>
+        <v>-0.04745343202901425</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.05794819836997608</v>
+        <v>-0.05166029574400281</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.06846042416195433</v>
+        <v>-0.07433332313047442</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1183932815393684</v>
+        <v>-0.09426316034470743</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06547768593246786</v>
+        <v>0.1637538891373547</v>
       </c>
     </row>
     <row r="14">
@@ -1546,79 +1551,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01553401393241825</v>
+        <v>-0.003396478924864653</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1477414665567885</v>
+        <v>-0.1643578835791269</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1243080758968476</v>
+        <v>-0.116244015524032</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.204303144622789</v>
+        <v>-0.211270508893957</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07297331408742871</v>
+        <v>-0.1229566269568241</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.05308321858780132</v>
+        <v>-0.0563967360925801</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008556450581249589</v>
+        <v>0.02000530832501556</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2645282050388944</v>
+        <v>-0.209616388299066</v>
       </c>
       <c r="J14" t="n">
-        <v>0.09562412730446343</v>
+        <v>0.06725138946045521</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03345736028417445</v>
+        <v>-0.003381483125568192</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.04375379667711657</v>
+        <v>-0.06150793389800161</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.009758001566214427</v>
+        <v>-0.00355459600083354</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.05526842810415941</v>
+        <v>-0.09060181580338984</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.09101916238838664</v>
+        <v>-0.07036866851210384</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.05082374677426008</v>
+        <v>-0.03990412256763717</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2007044310250382</v>
+        <v>-0.1959401062452802</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1325335135387244</v>
+        <v>0.008077576543886465</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02324565204706991</v>
+        <v>-0.06107454819798114</v>
       </c>
       <c r="U14" t="n">
-        <v>0.195125970958394</v>
+        <v>0.1621587341271487</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05434863605521403</v>
+        <v>0.0476672683919946</v>
       </c>
       <c r="W14" t="n">
-        <v>0.08520160377328828</v>
+        <v>0.07944226359398406</v>
       </c>
       <c r="X14" t="n">
-        <v>0.05908691891378462</v>
+        <v>0.05652973435891791</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02877798087585321</v>
+        <v>0.02520229893487505</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.04945558702845559</v>
+        <v>0.04708661311913308</v>
       </c>
     </row>
     <row r="15">
@@ -1628,79 +1633,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0005655748719153023</v>
+        <v>-0.002779112297835135</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.07523970361239991</v>
+        <v>-0.105278274886355</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1527020796631762</v>
+        <v>0.151238648892354</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1884037136266725</v>
+        <v>0.1690754715674055</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1733949111304422</v>
+        <v>0.1504613701187739</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.05736284762055232</v>
+        <v>-0.0873071141165865</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3309972341733941</v>
+        <v>0.333428578416301</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01162054789011406</v>
+        <v>0.04058994821967726</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3120693531502823</v>
+        <v>-0.3419733863567689</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09491633747282543</v>
+        <v>0.04254490698463638</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01590880241024032</v>
+        <v>-0.05446703898341512</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.126151370615202</v>
+        <v>-0.1431576596393079</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05526842810415941</v>
+        <v>-0.09060181580338984</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0804215229289342</v>
+        <v>0.1001827114559264</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07041107155608205</v>
+        <v>-0.06795109858139069</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2979485741482936</v>
+        <v>-0.3007696968246245</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1042819335072998</v>
+        <v>-0.1775178835401202</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03347822569925252</v>
+        <v>0.00149655255539094</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.02757365319018167</v>
+        <v>-0.07820775362069987</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01675484429476688</v>
+        <v>0.01697780426855979</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2487426171972664</v>
+        <v>-0.2681279989302652</v>
       </c>
       <c r="X15" t="n">
-        <v>0.07720437647766652</v>
+        <v>0.06629894111295374</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.05191680517205784</v>
+        <v>0.04643454699814573</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3247062261511431</v>
+        <v>0.08729962959276007</v>
       </c>
     </row>
     <row r="16">
@@ -1710,79 +1715,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.06239619098432448</v>
+        <v>-0.009540263633854828</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.03279852099146682</v>
+        <v>-0.02088983030982909</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004746345049572657</v>
+        <v>0.05545885841468199</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05937596725925919</v>
+        <v>-0.07374182133121257</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2471912202703344</v>
+        <v>0.2280079477596407</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03026885825778066</v>
+        <v>0.04883574954483194</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00279285414910758</v>
+        <v>0.03778354275267801</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05604576962883703</v>
+        <v>0.01847241792046498</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2474185011720835</v>
+        <v>-0.2588978531092331</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1145209701825497</v>
+        <v>-0.1151294319029593</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2026453869388183</v>
+        <v>-0.1917782991434748</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08888540727027135</v>
+        <v>-0.03699917494537475</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09101916238838664</v>
+        <v>-0.07036866851210384</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0804215229289342</v>
+        <v>0.1001827114559264</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1328863274903597</v>
+        <v>-0.0616144275583149</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07627728852515524</v>
+        <v>0.1195259036039978</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3090009714386777</v>
+        <v>-0.3910140029525035</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2323570916709441</v>
+        <v>-0.2048194672010449</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1963709268203715</v>
+        <v>-0.1853622716564137</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1610405238910213</v>
+        <v>-0.1035798289790734</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.008681196432105912</v>
+        <v>0.02895206647269854</v>
       </c>
       <c r="X16" t="n">
-        <v>0.001534921060092353</v>
+        <v>0.05213795113563746</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.05836885666048975</v>
+        <v>0.1006466638682504</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1006092279461699</v>
+        <v>-0.05713386383793941</v>
       </c>
     </row>
     <row r="17">
@@ -1792,79 +1797,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2642256559546799</v>
+        <v>-0.2554282692008578</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.009884059232415497</v>
+        <v>-0.0362056615885367</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1596506218579032</v>
+        <v>-0.1345390465847611</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03939947066283963</v>
+        <v>0.04432931012438374</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04163575432286039</v>
+        <v>0.04058511471636007</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1273479183509752</v>
+        <v>-0.1432489993336261</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1727674396077316</v>
+        <v>-0.1249044387211418</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2320282430384998</v>
+        <v>0.2749038422466645</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06150477941428651</v>
+        <v>0.005789445129930656</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.003501930630200548</v>
+        <v>-0.02640181206166841</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0006348033128858367</v>
+        <v>-0.009015545844369772</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1403713156891874</v>
+        <v>-0.1428650279191456</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05082374677426008</v>
+        <v>-0.03990412256763717</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.07041107155608205</v>
+        <v>-0.06795109858139069</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1328863274903597</v>
+        <v>-0.0616144275583149</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.06786398594440483</v>
+        <v>-0.05460974330821921</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.02920389435109275</v>
+        <v>-0.1979846599706008</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08672887319009645</v>
+        <v>0.1095259865468059</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0902279298424303</v>
+        <v>0.09452167551527992</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.02910784248514947</v>
+        <v>0.01632626505053304</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.09902467974271717</v>
+        <v>-0.07839184729899441</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1886863859377113</v>
+        <v>0.2018760992389481</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.06204287929803957</v>
+        <v>-0.0212845220740373</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.05402089596540785</v>
+        <v>-0.06965469532336498</v>
       </c>
     </row>
     <row r="18">
@@ -1874,79 +1879,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1115793390247838</v>
+        <v>-0.1021592610201006</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.01330990901069238</v>
+        <v>-0.01256893607328853</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3652684903218418</v>
+        <v>-0.326573467036564</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07733174147292698</v>
+        <v>0.07640183918839215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06125521483073013</v>
+        <v>0.0620620846008112</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02025442684803875</v>
+        <v>-0.00452445950181703</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2182026237715462</v>
+        <v>-0.1777530046403147</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1216443129806212</v>
+        <v>0.1354265045104489</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03789670336620722</v>
+        <v>-0.01978400455434953</v>
       </c>
       <c r="K18" t="n">
-        <v>0.05462772849810755</v>
+        <v>0.04130237446562691</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0253834451935978</v>
+        <v>0.01433628511027571</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.03650317742160974</v>
+        <v>-0.04195125954244813</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2007044310250382</v>
+        <v>-0.1959401062452802</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2979485741482936</v>
+        <v>-0.3007696968246245</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07627728852515524</v>
+        <v>0.1195259036039978</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.06786398594440483</v>
+        <v>-0.05460974330821921</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03971549053730172</v>
+        <v>-0.1168167964707499</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07482543500384889</v>
+        <v>-0.06414157905909709</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.07557013596523482</v>
+        <v>-0.0819833956910183</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1769925035590215</v>
+        <v>0.2088900990008025</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0582916643913582</v>
+        <v>-0.05187971272319605</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1187628765096929</v>
+        <v>-0.1095550901202651</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1252636284846152</v>
+        <v>-0.09038680487229411</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.1109779043518352</v>
+        <v>-0.1432115582806551</v>
       </c>
     </row>
     <row r="19">
@@ -1956,79 +1961,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03054837910556359</v>
+        <v>-0.06410689608143566</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2669242233955899</v>
+        <v>0.07405696530474856</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001168786775782443</v>
+        <v>-0.06600683732890779</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1356757383688977</v>
+        <v>-0.1101320671514192</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2961336219084621</v>
+        <v>0.1476940177145023</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1062525123426599</v>
+        <v>0.1236900071107781</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1916525319306796</v>
+        <v>-0.2657375093407782</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1941125033118677</v>
+        <v>-0.3261339621557808</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2353022320337063</v>
+        <v>0.2278883700378315</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2348301045663445</v>
+        <v>0.1660198022867714</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1158068014172114</v>
+        <v>0.07932373537019947</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0779738025129382</v>
+        <v>-0.08695806718091306</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1325335135387244</v>
+        <v>0.008077576543886465</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1042819335072998</v>
+        <v>-0.1775178835401202</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3090009714386777</v>
+        <v>-0.3910140029525035</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.02920389435109275</v>
+        <v>-0.1979846599706008</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03971549053730172</v>
+        <v>-0.1168167964707499</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2671110490314662</v>
+        <v>0.07489315537439957</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1060870171871635</v>
+        <v>0.0338485312854015</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2300395117370396</v>
+        <v>-0.2491905810151794</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.07517165373673775</v>
+        <v>0.06648626667462997</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.08470411652743837</v>
+        <v>-0.1741534250216515</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01075977476992876</v>
+        <v>-0.08895125517180204</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0001575526043004591</v>
+        <v>0.1537847665110656</v>
       </c>
     </row>
     <row r="20">
@@ -2038,79 +2043,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2721094632221182</v>
+        <v>-0.2611878242447249</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.06784863835372863</v>
+        <v>-0.08791220084457049</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1098417375980897</v>
+        <v>0.1239915997002966</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2039408881056791</v>
+        <v>0.1702869188538705</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2035802865464004</v>
+        <v>0.1619964973706571</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1395559674126733</v>
+        <v>-0.1603512580397853</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08587297415235542</v>
+        <v>0.08066034443584041</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1541690587360727</v>
+        <v>-0.123285981019245</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0394918760778257</v>
+        <v>0.005438300193768845</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03836728236635845</v>
+        <v>-0.008779392495777394</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01931574660041992</v>
+        <v>-0.02107951123937241</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1041292160397365</v>
+        <v>-0.0980968938908678</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.02324565204706991</v>
+        <v>-0.06107454819798114</v>
       </c>
       <c r="O20" t="n">
-        <v>0.03347822569925252</v>
+        <v>0.00149655255539094</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2323570916709441</v>
+        <v>-0.2048194672010449</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.08672887319009645</v>
+        <v>0.1095259865468059</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.07482543500384889</v>
+        <v>-0.06414157905909709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2671110490314662</v>
+        <v>0.07489315537439957</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1887210049126365</v>
+        <v>0.1449433097873712</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1132529457674971</v>
+        <v>0.1190716085826149</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.07557632808374143</v>
+        <v>-0.087421855533332</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.03013279783894338</v>
+        <v>-0.02630425959788597</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1216950058862366</v>
+        <v>-0.1238735531933618</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.02639735315595606</v>
+        <v>-0.2246724515280555</v>
       </c>
     </row>
     <row r="21">
@@ -2120,79 +2125,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1057033273050682</v>
+        <v>-0.1058716071754058</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.02614132734557088</v>
+        <v>-0.05206028030497072</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1142290661976083</v>
+        <v>-0.1175758073771253</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.242548939420619</v>
+        <v>-0.2639045560333244</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1087047597598104</v>
+        <v>-0.1691567807682262</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.25066660898599</v>
+        <v>-0.2763621633747501</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1113668570528427</v>
+        <v>0.1113597264011574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1436164437751536</v>
+        <v>-0.1089409202440981</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2487036336732334</v>
+        <v>0.2153853175853401</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3057493593159705</v>
+        <v>-0.3809435574117781</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3012876912512547</v>
+        <v>-0.3465757365504366</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1235280895570446</v>
+        <v>0.1236009637655076</v>
       </c>
       <c r="N21" t="n">
-        <v>0.195125970958394</v>
+        <v>0.1621587341271487</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.02757365319018167</v>
+        <v>-0.07820775362069987</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1963709268203715</v>
+        <v>-0.1853622716564137</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0902279298424303</v>
+        <v>0.09452167551527992</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.07557013596523482</v>
+        <v>-0.0819833956910183</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1060870171871635</v>
+        <v>0.0338485312854015</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1887210049126365</v>
+        <v>0.1449433097873712</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3259323454849154</v>
+        <v>0.3149007617626724</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1301714071343776</v>
+        <v>0.1131331117491272</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2044904980925609</v>
+        <v>-0.2238067944969593</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06698300093908854</v>
+        <v>0.05303778170359207</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.1742613927658219</v>
+        <v>0.05770237939417494</v>
       </c>
     </row>
     <row r="22">
@@ -2202,79 +2207,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1142298174413352</v>
+        <v>-0.08130713382084868</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1391142918175761</v>
+        <v>-0.1292729791903385</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3125273264741198</v>
+        <v>-0.2639081178532762</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1524956806022614</v>
+        <v>-0.1469323170959278</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09487991186943991</v>
+        <v>-0.1079007107644815</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07676344073232731</v>
+        <v>-0.08971142734917244</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1405695950946956</v>
+        <v>0.1556914280446103</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.014895259375718</v>
+        <v>0.02786153280055019</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1466227388328502</v>
+        <v>0.09925825500038475</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2065883818473965</v>
+        <v>-0.2345752253997641</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2876849930437493</v>
+        <v>-0.3023718356585228</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07425815230967063</v>
+        <v>-0.04745343202901425</v>
       </c>
       <c r="N22" t="n">
-        <v>0.05434863605521403</v>
+        <v>0.0476672683919946</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01675484429476688</v>
+        <v>0.01697780426855979</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1610405238910213</v>
+        <v>-0.1035798289790734</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.02910784248514947</v>
+        <v>0.01632626505053304</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1769925035590215</v>
+        <v>0.2088900990008025</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2300395117370396</v>
+        <v>-0.2491905810151794</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1132529457674971</v>
+        <v>0.1190716085826149</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3259323454849154</v>
+        <v>0.3149007617626724</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1454215611918736</v>
+        <v>-0.1304928797915665</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1710939965490758</v>
+        <v>-0.1378040724959919</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.1779817605262802</v>
+        <v>-0.1447389553910438</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.1607509210667817</v>
+        <v>-0.002893477860266542</v>
       </c>
     </row>
     <row r="23">
@@ -2284,79 +2289,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1283990469538358</v>
+        <v>-0.1156483488664906</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.06310892628439439</v>
+        <v>-0.08160400171389084</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1303628752636095</v>
+        <v>0.1381469127455254</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3667370445127645</v>
+        <v>-0.3826720789498251</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03320538397405379</v>
+        <v>0.004866338952331471</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1525620104773109</v>
+        <v>0.1525065921900172</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1064125475694993</v>
+        <v>-0.08361823886933628</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3748112424556149</v>
+        <v>-0.2999498258179474</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03584881566329622</v>
+        <v>0.00482752895915282</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3123827828609161</v>
+        <v>-0.3485250494193273</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1724437781679148</v>
+        <v>-0.1823059053769813</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.05794819836997608</v>
+        <v>-0.05166029574400281</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08520160377328828</v>
+        <v>0.07944226359398406</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2487426171972664</v>
+        <v>-0.2681279989302652</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.008681196432105912</v>
+        <v>0.02895206647269854</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.09902467974271717</v>
+        <v>-0.07839184729899441</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.0582916643913582</v>
+        <v>-0.05187971272319605</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.07517165373673775</v>
+        <v>0.06648626667462997</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07557632808374143</v>
+        <v>-0.087421855533332</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1301714071343776</v>
+        <v>0.1131331117491272</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1454215611918736</v>
+        <v>-0.1304928797915665</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1948470305610225</v>
+        <v>-0.1846578319516758</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5416712412035921</v>
+        <v>0.5466907630470584</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1189248163909895</v>
+        <v>-0.06919034502533444</v>
       </c>
     </row>
     <row r="24">
@@ -2366,79 +2371,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.03267497664441223</v>
+        <v>-0.029433496549341</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0325681507773059</v>
+        <v>-0.0601361082288161</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09366466586728024</v>
+        <v>0.1040410638966982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07274049467139727</v>
+        <v>0.07418123108440784</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07293333438927646</v>
+        <v>0.06742330807065183</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2026430399487932</v>
+        <v>-0.2219472019119165</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3451352046263638</v>
+        <v>-0.308037088935587</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1767747392059384</v>
+        <v>0.2198549784779854</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.10688462729661</v>
+        <v>-0.1476541273146562</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1256898600927265</v>
+        <v>0.09291841897282982</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.03488712500007909</v>
+        <v>-0.0522783272541282</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.06846042416195433</v>
+        <v>-0.07433332313047442</v>
       </c>
       <c r="N24" t="n">
-        <v>0.05908691891378462</v>
+        <v>0.05652973435891791</v>
       </c>
       <c r="O24" t="n">
-        <v>0.07720437647766652</v>
+        <v>0.06629894111295374</v>
       </c>
       <c r="P24" t="n">
-        <v>0.001534921060092353</v>
+        <v>0.05213795113563746</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1886863859377113</v>
+        <v>0.2018760992389481</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.1187628765096929</v>
+        <v>-0.1095550901202651</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.08470411652743837</v>
+        <v>-0.1741534250216515</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.03013279783894338</v>
+        <v>-0.02630425959788597</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2044904980925609</v>
+        <v>-0.2238067944969593</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1710939965490758</v>
+        <v>-0.1378040724959919</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1948470305610225</v>
+        <v>-0.1846578319516758</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.03029876013027495</v>
+        <v>-0.006280446924301622</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.07150351564061533</v>
+        <v>0.006612555976300918</v>
       </c>
     </row>
     <row r="25">
@@ -2448,79 +2453,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2520675978436042</v>
+        <v>-0.2207260158334451</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1650420717119973</v>
+        <v>-0.1584312442011695</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1483978835371393</v>
+        <v>0.1741072247040596</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1484258321862043</v>
+        <v>-0.1402427128490653</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.07508356364663261</v>
+        <v>-0.09375754423229749</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01445641311303298</v>
+        <v>0.01235105852821646</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1120414616068364</v>
+        <v>0.1311271106285613</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0826535155641706</v>
+        <v>-0.02398004170597763</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1231712329800701</v>
+        <v>-0.1487430310115122</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2243689674152028</v>
+        <v>-0.2539109220770367</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3579994878714218</v>
+        <v>-0.3667157424923509</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1183932815393684</v>
+        <v>-0.09426316034470743</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02877798087585321</v>
+        <v>0.02520229893487505</v>
       </c>
       <c r="O25" t="n">
-        <v>0.05191680517205784</v>
+        <v>0.04643454699814573</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05836885666048975</v>
+        <v>0.1006466638682504</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.06204287929803957</v>
+        <v>-0.0212845220740373</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1252636284846152</v>
+        <v>-0.09038680487229411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.01075977476992876</v>
+        <v>-0.08895125517180204</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1216950058862366</v>
+        <v>-0.1238735531933618</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06698300093908854</v>
+        <v>0.05303778170359207</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1779817605262802</v>
+        <v>-0.1447389553910438</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5416712412035921</v>
+        <v>0.5466907630470584</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.03029876013027495</v>
+        <v>-0.006280446924301622</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.05732465688484165</v>
+        <v>-0.1694829739315444</v>
       </c>
     </row>
     <row r="26">
@@ -2530,76 +2535,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.06525572386233182</v>
+        <v>-0.1341674741568012</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.08653404935448977</v>
+        <v>-0.1092641382210543</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03769113220606555</v>
+        <v>-0.1381433661314109</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.04848076034591595</v>
+        <v>0.01068755160722421</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.02284565087764485</v>
+        <v>0.008465930079086728</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.02084473619392829</v>
+        <v>-0.06480687681912249</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08278260237290894</v>
+        <v>-0.1182930324070627</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1442935911488702</v>
+        <v>-0.1451779590810106</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06005872321767792</v>
+        <v>0.1431949440172071</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1527679788991687</v>
+        <v>-0.05417102469947842</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.04283451957315779</v>
+        <v>0.03060519538109467</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06547768593246786</v>
+        <v>0.1637538891373547</v>
       </c>
       <c r="N26" t="n">
-        <v>0.04945558702845559</v>
+        <v>0.04708661311913308</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3247062261511431</v>
+        <v>0.08729962959276007</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1006092279461699</v>
+        <v>-0.05713386383793941</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.05402089596540785</v>
+        <v>-0.06965469532336498</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.1109779043518352</v>
+        <v>-0.1432115582806551</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0001575526043004591</v>
+        <v>0.1537847665110656</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.02639735315595606</v>
+        <v>-0.2246724515280555</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1742613927658219</v>
+        <v>0.05770237939417494</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1607509210667817</v>
+        <v>-0.002893477860266542</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1189248163909895</v>
+        <v>-0.06919034502533444</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.07150351564061533</v>
+        <v>0.006612555976300918</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.05732465688484165</v>
+        <v>-0.1694829739315444</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
